--- a/files/schedule_modules.xlsx
+++ b/files/schedule_modules.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jessicacooperstone/Documents/git/rdataviz/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jessicacooperstone/git/rdataviz/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74168391-F080-FB42-B2D3-842DE9D8D2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E585AACF-C814-8C42-B124-3E139AA782B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22400" yWindow="2540" windowWidth="28800" windowHeight="16360" activeTab="1" xr2:uid="{21EBE61F-A4F0-3D45-865A-9EB87E85AA6A}"/>
+    <workbookView xWindow="20980" yWindow="1900" windowWidth="28800" windowHeight="16360" activeTab="1" xr2:uid="{21EBE61F-A4F0-3D45-865A-9EB87E85AA6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="2" r:id="rId1"/>
-    <sheet name="Schedule_date_2025" sheetId="7" r:id="rId2"/>
-    <sheet name="module_due_dates_2025" sheetId="8" r:id="rId3"/>
-    <sheet name="Schedule_date_2024" sheetId="5" r:id="rId4"/>
-    <sheet name="module_due_dates_2024" sheetId="6" r:id="rId5"/>
-    <sheet name="Schedule_date_2023" sheetId="3" r:id="rId6"/>
-    <sheet name="module_due_dates_2023" sheetId="4" r:id="rId7"/>
+    <sheet name="Schedule_date_2026" sheetId="9" r:id="rId2"/>
+    <sheet name="module_due_dates_2026" sheetId="10" r:id="rId3"/>
+    <sheet name="Schedule_date_2025" sheetId="7" r:id="rId4"/>
+    <sheet name="module_due_dates_2025" sheetId="8" r:id="rId5"/>
+    <sheet name="Schedule_date_2024" sheetId="5" r:id="rId6"/>
+    <sheet name="module_due_dates_2024" sheetId="6" r:id="rId7"/>
+    <sheet name="Schedule_date_2023" sheetId="3" r:id="rId8"/>
+    <sheet name="module_due_dates_2023" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="60">
   <si>
     <t>Principles of data visualization</t>
   </si>
@@ -213,14 +215,24 @@
   </si>
   <si>
     <t>Manhattan plots and making lots of plots at once (asynchronous)</t>
+  </si>
+  <si>
+    <t>Principles of data visualization 1</t>
+  </si>
+  <si>
+    <t>Principles of data visualization 2</t>
+  </si>
+  <si>
+    <t>ggplot extension packages (asynchronous)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -251,12 +263,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -770,6 +785,369 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58EC1E5-6A88-8047-9F93-0FC211E68D53}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46273</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46280</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46287</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46294</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46301</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46315</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46322</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46329</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46336</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46343</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46350</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46357</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46364</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H18" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EACCAF-8C8B-E146-ABA1-005F5C4A7B4F}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5">
+        <f>Schedule_date_2026!B4 + -1</f>
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5">
+        <f>Schedule_date_2026!B9</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5">
+        <f>Schedule_date_2026!B12</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5">
+        <f>Schedule_date_2026!B17</f>
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5">
+        <f>Schedule_date_2026!B13</f>
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5">
+        <f>Schedule_date_2026!B17+5</f>
+        <v>46369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D2FBAB-5424-1A47-B52E-30F77FDEB3FC}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -986,7 +1364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07222E7-34D9-A648-B0D9-7893E36781B6}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1073,7 +1451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E7002E-0E54-7A4A-93D0-B7490C5E682B}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1290,7 +1668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB6305A-7A3D-E944-958B-BA084CA13D72}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1369,7 +1747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AC0B77-377C-2E43-B142-D9BC271E0496}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1570,7 +1948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48504950-6619-024D-BFE6-3D795EC0E695}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/files/schedule_modules.xlsx
+++ b/files/schedule_modules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jessicacooperstone/git/rdataviz/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E585AACF-C814-8C42-B124-3E139AA782B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC4A8C7-1E71-CF4D-84CB-D36E5B9D68E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20980" yWindow="1900" windowWidth="28800" windowHeight="16360" activeTab="1" xr2:uid="{21EBE61F-A4F0-3D45-865A-9EB87E85AA6A}"/>
+    <workbookView xWindow="17480" yWindow="2380" windowWidth="28800" windowHeight="16360" activeTab="2" xr2:uid="{21EBE61F-A4F0-3D45-865A-9EB87E85AA6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="67">
   <si>
     <t>Principles of data visualization</t>
   </si>
@@ -224,6 +224,27 @@
   </si>
   <si>
     <t>ggplot extension packages (asynchronous)</t>
+  </si>
+  <si>
+    <t>Monday, September 7, 2026</t>
+  </si>
+  <si>
+    <t>Tuesday, October 13, 2026</t>
+  </si>
+  <si>
+    <t>Tuesday, November 3, 2026</t>
+  </si>
+  <si>
+    <t>Tuesday, December 8, 2026</t>
+  </si>
+  <si>
+    <t>Tuesday, November 10, 2026</t>
+  </si>
+  <si>
+    <t>Sunday, December 13, 2026</t>
+  </si>
+  <si>
+    <t>due_date_paste</t>
   </si>
 </sst>
 </file>
@@ -232,7 +253,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -269,7 +290,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1056,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EACCAF-8C8B-E146-ABA1-005F5C4A7B4F}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" bestFit="1" customWidth="1"/>
@@ -1064,31 +1085,40 @@
     <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1096,8 +1126,11 @@
         <f>Schedule_date_2026!B4 + -1</f>
         <v>46272</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1105,8 +1138,11 @@
         <f>Schedule_date_2026!B9</f>
         <v>46308</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1114,8 +1150,11 @@
         <f>Schedule_date_2026!B12</f>
         <v>46329</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1123,8 +1162,11 @@
         <f>Schedule_date_2026!B17</f>
         <v>46364</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1132,14 +1174,20 @@
         <f>Schedule_date_2026!B13</f>
         <v>46336</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="5">
         <f>Schedule_date_2026!B17+5</f>
         <v>46369</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
